--- a/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,54</t>
+          <t>-3,38; 5,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 4,46</t>
+          <t>-6,16; 4,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 12,27</t>
+          <t>-0,01; 12,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 2,07</t>
+          <t>-8,83; 2,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,73; 499,54</t>
+          <t>-70,25; 549,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,11; 475,21</t>
+          <t>-80,67; 400,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,92</t>
+          <t>-1,41; 1,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,35</t>
+          <t>-1,58; 1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,08</t>
+          <t>-2,23; 0,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,59</t>
+          <t>-3,33; 0,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 124,57</t>
+          <t>-44,89; 129,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 101,01</t>
+          <t>-54,76; 98,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 64,03</t>
+          <t>-65,11; 56,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 32,46</t>
+          <t>-73,61; 14,3</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 3,07</t>
+          <t>-3,63; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; -0,96</t>
+          <t>-5,8; -0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,26</t>
+          <t>-3,9; 0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 2,26</t>
+          <t>-7,79; 2,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,98; 174,66</t>
+          <t>-72,08; 163,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,9</t>
+          <t>-100,0; 66,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 260,35</t>
+          <t>-100,0; 234,73</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,68</t>
+          <t>-1,07; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,5</t>
+          <t>-2,07; 0,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,03</t>
+          <t>-1,68; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,11</t>
+          <t>-3,26; 0,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 78,41</t>
+          <t>-35,32; 85,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 27,63</t>
+          <t>-61,89; 26,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 51,19</t>
+          <t>-50,03; 50,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,96; 8,56</t>
+          <t>-69,35; 17,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 5,5</t>
+          <t>-3,23; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 4,17</t>
+          <t>-5,85; 4,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,29</t>
+          <t>-0,1; 12,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 2,17</t>
+          <t>-8,34; 2,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 549,29</t>
+          <t>-71,78; 507,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,67; 400,54</t>
+          <t>-82,74; 391,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,16; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,97</t>
+          <t>-1,12; 2,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,4</t>
+          <t>-1,82; 1,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,98</t>
+          <t>-2,2; 0,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,38</t>
+          <t>-3,39; 0,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 129,81</t>
+          <t>-39,45; 137,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 98,12</t>
+          <t>-61,5; 98,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 56,04</t>
+          <t>-62,11; 64,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 14,3</t>
+          <t>-72,51; 13,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,13</t>
+          <t>-3,47; 2,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,99</t>
+          <t>-5,85; -1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,37</t>
+          <t>-4,29; 0,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 2,15</t>
+          <t>-8,62; 2,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 163,89</t>
+          <t>-68,09; 156,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,02</t>
+          <t>-100,0; -4,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,99</t>
+          <t>-100,0; 54,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,73</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,81</t>
+          <t>-1,05; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,47</t>
+          <t>-2,21; 0,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,93</t>
+          <t>-1,66; 1,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,3</t>
+          <t>-3,29; 0,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 85,92</t>
+          <t>-31,4; 84,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,89; 26,54</t>
+          <t>-64,17; 29,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 50,12</t>
+          <t>-50,5; 63,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,35; 17,82</t>
+          <t>-69,86; 8,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-63,48%</t>
+          <t>-59,13%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 5,69</t>
+          <t>-3,24; 5,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 4,91</t>
+          <t>-6,08; 4,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 12,54</t>
+          <t>0,19; 12,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 2,49</t>
+          <t>-9,05; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,78; 507,41</t>
+          <t>-69,73; 499,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,74; 391,14</t>
+          <t>-87,11; 475,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-75,16; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-40,0%</t>
+          <t>-36,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,07</t>
+          <t>-1,3; 1,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,41</t>
+          <t>-1,72; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,97</t>
+          <t>-2,26; 1,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,26</t>
+          <t>-3,36; 0,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 137,47</t>
+          <t>-43,86; 124,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 98,18</t>
+          <t>-56,35; 101,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 64,92</t>
+          <t>-62,58; 64,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 13,63</t>
+          <t>-68,51; 34,36</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-32,9%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,68</t>
+          <t>-3,61; 3,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -1,03</t>
+          <t>-5,65; -0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,32</t>
+          <t>-4,15; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 2,23</t>
+          <t>-3,1; 2,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 156,46</t>
+          <t>-68,98; 174,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,88</t>
+          <t>-100,0; 59,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,61; 388,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-40,44%</t>
+          <t>-30,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,78</t>
+          <t>-1,12; 1,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,48</t>
+          <t>-2,01; 0,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,09</t>
+          <t>-1,66; 1,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,14</t>
+          <t>-2,7; 0,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 84,46</t>
+          <t>-32,97; 78,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 29,35</t>
+          <t>-59,55; 27,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 63,33</t>
+          <t>-50,94; 51,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 8,59</t>
+          <t>-61,8; 31,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-11,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>269,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-59,13%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.141320750341832</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4971175903550729</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.053159061537403</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.483928933693935</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.360759744788672</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1144200645101375</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2.698668817171904</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5913094218238789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,24; 5,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,08; 4,46</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,19; 12,27</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-9,05; 2,95</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-69,73; 499,54</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-87,11; 475,21</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.24053641602583</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.079632627737109</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1878161534170517</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.048561225843478</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6973140562568733</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8711166414494107</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.543596779771332</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.455698220817348</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.27198008826903</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.950623268734777</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4.995437324451583</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>4.752139079038242</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-7,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-22,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-36,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,3; 1,92</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,72; 1,35</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 1,08</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,36; 0,75</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-43,86; 124,57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-56,35; 101,01</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-62,58; 64,03</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-68,51; 34,36</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.3389310874824268</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.1694673820802292</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6048579885837325</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.327643402964557</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1474711522404413</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.07448001623722002</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.2237552174394301</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.361265581598847</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-7,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-91,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-60,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.301693962019129</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.71729320904478</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.260086014350623</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.355164203359231</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4386048897531817</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5635047677739218</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6257874856089054</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6851120291972362</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,61; 3,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,65; -0,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 0,26</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,1; 2,99</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-68,98; 174,66</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 59,9</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-83,61; 388,74</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.91688610898476</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.346075309103279</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.076939734804513</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.7465043078497667</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.245669232251601</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.01010739075606</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.640270209125964</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3436493319166302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +811,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-28,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-13,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-30,96%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.274266151670955</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.743189324184574</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.530316224068741</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.236387892770501</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.0779155327789892</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.9110500375017964</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.6032234306006302</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1073099524174887</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,12; 1,68</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,01; 0,5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 1,03</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 0,58</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-32,97; 78,41</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-59,55; 27,63</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-50,94; 51,19</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-61,8; 31,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.605757354881935</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.649286859348812</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.150016105965039</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.104321666841302</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6898443134806777</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8361228574701699</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.074713111314439</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.962399118904628</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2630521396679225</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.989793266540346</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.74658836483987</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>0.5990081972496932</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>3.887438197445343</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3452999846223933</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.772744790465596</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3472149470705965</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.041416304406382</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1293263282117804</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2888640876017947</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1343284913305255</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.309598268441789</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.116191043064287</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.006058078580936</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.659850253478587</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.700266899481161</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3296806641600014</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.595485075064896</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5094030581038214</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6180414577626908</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.675227107987798</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5038613783494054</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.030436157666736</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.5816010879707668</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7841358577127046</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2763340392215465</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5118708275832577</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3163657035097613</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1005,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
